--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GIK32M</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GIK38J</t>
+          <t>GIK32M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -735,19 +735,19 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GMA2ZT</t>
+          <t>GIK376</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,120 +757,120 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2ZT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK38G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38G</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK38J</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38J</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GMA2ZT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2ZT</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
+          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
+          <t>17 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
+          <t>24 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,110 +1238,110 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMT338</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT338</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
+          <t>32 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
+          <t>77 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,132 +1351,132 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
+          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
+          <t>45 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMT3J2</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>77 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GMT3J3</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>17 lärandemål (maximum rekommenderat: 12)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
+          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AEG2C5</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,78 +1513,78 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GMT338</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT338</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,51 +1648,51 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GEG38F</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG38F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GEG3DU</t>
+          <t>GMT3J2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1707,19 +1707,19 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSQ25F</t>
+          <t>GMT3J3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1734,93 +1734,741 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>GMT3JV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+          <t>1 lärandemål (minimum rekommenderat: 4)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>MT1074</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>MT2006</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>AEG225</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>AEG233</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AV</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AV</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AEG2C5</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>EG3007</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>EG3009</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>EG3020</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>EG3022</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GEG26J</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GEG38F</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG38F</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GEG3DU</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DU</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23J</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25F</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>För få mål</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E51"/>
+  <autoFilter ref="A1:E75"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1922,6 +2570,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$75</definedName>

--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$75</definedName>

--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABY22V</t>
+          <t>BY1054</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABY22V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1054</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ABY27W</t>
+          <t>BY1061</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABY27W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1061</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BY1054</t>
+          <t>GBY2MA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BY3004</t>
+          <t>GBY2NF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,56 +563,56 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GBY2NG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29 ord: - Praktiskt konfigurera och implementera tekniker som möjliggör trådlös kommunik…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GBY2RN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,78 +622,78 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GBY2RX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -703,127 +703,127 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
+          <t>29 ord: - Praktiskt konfigurera och implementera tekniker som möjliggör trådlös kommunik…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GIK32M</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GIK376</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GIK38G</t>
+          <t>GIE3JG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GIK38J</t>
+          <t>GIE3JH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK38J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,110 +833,110 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GMA2ZT</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2ZT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,78 +946,78 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
+          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,51 +1027,51 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,105 +1081,105 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
+          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GIK34Y</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>GIK376</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>28 lärandemål (maximum rekommenderat: 12)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>GIK3BY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,51 +1189,51 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,51 +1243,51 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 12)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMD33X</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>45 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,56 +1535,56 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GMT338</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT338</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,78 +1594,78 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
+          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
+          <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,213 +1675,213 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GMT3J2</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GMT3J3</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GMT3JV</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 4)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MT1074</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,132 +1891,132 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
+          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
+          <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AEG2AV</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AEG2C5</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,105 +2026,105 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
+          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,105 +2134,105 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
+          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GMT344</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>GMT349</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,78 +2242,78 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
+          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GEG38F</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG38F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GEG3DU</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,51 +2323,51 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>1 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3DU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSQ23J</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSQ25F</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,44 +2431,395 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>EG3007</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>EG3009</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>EG3020</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>EG3022</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23J</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E75"/>
+  <autoFilter ref="A1:E88"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2618,6 +2969,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -661,12 +661,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GDT2JM</t>
+          <t>GBY342</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY342</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,51 +698,51 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29 ord: - Praktiskt konfigurera och implementera tekniker som möjliggör trådlös kommunik…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
+          <t>29 ord: - Praktiskt konfigurera och implementera tekniker som möjliggör trådlös kommunik…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GIE3JG</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GIE3JH</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GIE3JG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -843,19 +843,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GIE3JH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
+          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -978,14 +978,14 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIK34Y</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIK376</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIK3BY</t>
+          <t>GIK34Y</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>GIK376</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>GIK3BY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,29 +1265,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,39 +1351,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
+          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
+          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
+          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GMD33X</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
+          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,78 +2048,78 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GMT344</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2166,14 +2166,14 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GMT349</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GMT344</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GMT349</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
+          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1 lärandemål (minimum rekommenderat: 3 för 2 hp)</t>
+          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,78 +2345,78 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>GMT3J4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 2.5 hp)</t>
+          <t>5 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
+          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>AEG294</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
+          <t>6 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
+          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
+          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
+          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
+          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSQ23J</t>
+          <t>EG3020</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>EG3022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,44 +2782,125 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>GSQ23J</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E88"/>
+  <autoFilter ref="A1:E91"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2995,6 +3076,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,115 +472,115 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BY1054</t>
+          <t>FDA222R</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>ANALYTIC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222R</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BY1061</t>
+          <t>FDA222S</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>ANALYTIC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 4 för 10 hp)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GBY2MA</t>
+          <t>FDA222T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>ANALYTIC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222T</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GBY2NF</t>
+          <t>FDA222U</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>ANALYTIC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222U</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GBY2NG</t>
+          <t>BY1054</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1054</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GBY2RN</t>
+          <t>BY1061</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1061</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GBY2RX</t>
+          <t>GBY2MA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GBY342</t>
+          <t>GBY2NF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY342</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GDT2JM</t>
+          <t>GBY2NG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -708,46 +708,46 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GBY2RN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29 ord: - Praktiskt konfigurera och implementera tekniker som möjliggör trådlös kommunik…</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>GBY2RX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>GBY342</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY342</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,159 +811,159 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GIE3JG</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - Praktiskt konfigurera och implementera tekniker som möjliggör trådlös kommunik…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIE3JH</t>
+          <t>FEB222K</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222K</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>FEB222L</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>FEB222M</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 1 för 3 hp)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>FEB222P</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 4.5 hp)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222P</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,51 +973,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>GIE3JG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GIE3JH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1113,14 +1113,14 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIK34Y</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIK376</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIK3BY</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1329,46 +1329,46 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK34Y</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,132 +1405,132 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK376</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK3BY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,73 +1540,73 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
+          <t>11 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GMD33X</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,29 +2102,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,78 +2134,78 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
+          <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GMT344</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,51 +2215,51 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GMT349</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,159 +2296,159 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
+          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>FMI2222</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GMT3J4</t>
+          <t>FMI2223</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2223</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>MIKR002</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - värdera olika typer av uppgifter och typer av datainsamling med avseende på di…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AEG294</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,78 +2485,78 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
+          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>GMT344</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>GMT349</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,73 +2647,73 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
+          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GMT3J4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
+          <t>5 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>AEG294</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+          <t>6 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
+          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSQ23J</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,71 +2836,368 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>EG3020</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>EG3022</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23J</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
         <is>
           <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E91"/>
+  <autoFilter ref="A1:E102"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3082,6 +3379,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222R</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 4 för 10 hp)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222T</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222U</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2014-08-28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1054</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2015-11-23</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1061</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
         </is>
@@ -779,15 +857,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY342</t>
         </is>
@@ -806,15 +890,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
@@ -833,15 +923,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>29 ord: - Praktiskt konfigurera och implementera tekniker som möjliggör trådlös kommunik…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
@@ -860,15 +956,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222K</t>
         </is>
@@ -887,15 +989,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
         </is>
@@ -914,15 +1022,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 1 för 3 hp)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222M</t>
         </is>
@@ -941,15 +1055,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>7 lärandemål (maximum rekommenderat: 6 för 4.5 hp)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222P</t>
         </is>
@@ -968,15 +1088,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
@@ -995,15 +1121,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2022-12-13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
@@ -1022,15 +1154,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2022-12-13</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
@@ -1049,15 +1187,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
         </is>
@@ -1076,15 +1220,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
         </is>
@@ -1103,15 +1253,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2019-04-29</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
@@ -1130,15 +1286,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2019-02-21</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
@@ -1157,15 +1319,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2018-10-11</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
@@ -1184,15 +1352,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2019-04-18</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
@@ -1211,15 +1385,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
@@ -1238,15 +1418,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
@@ -1265,15 +1451,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
@@ -1292,15 +1484,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
@@ -1319,15 +1517,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2021-04-15</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
@@ -1346,15 +1550,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
@@ -1373,15 +1583,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
@@ -1400,15 +1616,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
         </is>
@@ -1427,15 +1649,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
         </is>
@@ -1454,15 +1682,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
         </is>
@@ -1481,15 +1715,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>2007-06-13</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
@@ -1508,15 +1748,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>2013-02-21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
@@ -1535,15 +1785,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2013-03-14</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
@@ -1562,15 +1818,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2020-03-04</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
@@ -1589,15 +1851,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2017-02-16</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
@@ -1616,15 +1884,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
@@ -1643,15 +1917,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
@@ -1670,15 +1950,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
@@ -1697,15 +1983,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
@@ -1724,15 +2016,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
@@ -1751,15 +2049,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
@@ -1778,15 +2082,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
@@ -1805,15 +2115,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
@@ -1832,15 +2148,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
@@ -1859,15 +2181,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
@@ -1886,15 +2214,25 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
@@ -1913,15 +2251,25 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>2020-04-08</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
@@ -1940,15 +2288,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>2020-04-08</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
@@ -1967,15 +2325,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>2020-04-08</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
@@ -1994,15 +2362,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>2020-04-08</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
@@ -2021,15 +2399,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
@@ -2048,15 +2432,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
@@ -2075,15 +2469,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
@@ -2102,15 +2506,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
@@ -2129,15 +2543,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
@@ -2156,15 +2576,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
@@ -2183,15 +2609,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
@@ -2210,15 +2642,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
@@ -2237,15 +2675,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
@@ -2264,15 +2708,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
@@ -2291,15 +2741,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
@@ -2318,15 +2774,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
@@ -2345,15 +2807,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
         </is>
@@ -2372,15 +2840,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>2017-10-04</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>För få mål</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2223</t>
         </is>
@@ -2399,15 +2873,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>2012-12-04</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>26 ord: - värdera olika typer av uppgifter och typer av datainsamling med avseende på di…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
         </is>
@@ -2426,15 +2906,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2018-04-05</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
@@ -2453,15 +2939,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
@@ -2480,15 +2972,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
@@ -2507,15 +3005,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
         </is>
@@ -2534,15 +3038,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
         </is>
@@ -2561,15 +3071,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
@@ -2588,15 +3104,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
@@ -2615,15 +3137,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
@@ -2642,15 +3170,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
@@ -2669,15 +3203,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>5 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
         </is>
@@ -2696,15 +3236,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2014-04-03</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
@@ -2723,15 +3269,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>2019-06-05</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
@@ -2750,15 +3302,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>6 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
         </is>
@@ -2777,15 +3335,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
@@ -2804,15 +3368,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
@@ -2831,15 +3401,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
@@ -2858,15 +3434,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
@@ -2885,15 +3467,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
@@ -2912,15 +3500,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
@@ -2939,15 +3533,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
@@ -2966,15 +3566,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
@@ -2993,15 +3599,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>2015-08-27</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
@@ -3020,15 +3632,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>2017-12-14</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
@@ -3047,15 +3665,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
@@ -3074,15 +3698,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>2014-11-27</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
@@ -3101,15 +3731,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>2018-05-24</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
@@ -3128,15 +3764,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
@@ -3155,15 +3797,25 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>2011-02-15</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2012-11-07</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
         </is>
@@ -3182,225 +3834,231 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>2011-12-08</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E102"/>
+  <autoFilter ref="A1:G102"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -946,40 +946,40 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FEB222K</t>
+          <t>GDV3KY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ENERGIBM</t>
+          <t>DVE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
+          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDV3KY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FEB222L</t>
+          <t>FEB222K</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,14 +1005,14 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222K</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FEB222M</t>
+          <t>FEB222L</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1033,19 +1033,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 1 för 3 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 2 för 5 hp)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FEB222P</t>
+          <t>FEB222M</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1055,40 +1055,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7 lärandemål (maximum rekommenderat: 6 för 4.5 hp)</t>
+          <t>0 lärandemål (minimum rekommenderat: 1 för 3 hp)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>FEB222P</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>ENERGIBM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1099,19 +1099,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 4.5 hp)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222P</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2022-12-13</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1132,19 +1132,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1165,29 +1165,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 10 för 10 hp)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GIE3JG</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2022-12-13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1198,19 +1198,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GIE3JH</t>
+          <t>GIE3JG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1231,29 +1231,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GIE3JH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2019-04-29</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1264,19 +1264,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2019-04-29</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1297,19 +1297,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1319,30 +1319,30 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2018-10-11</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
+          <t>14 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2019-04-18</t>
+          <t>2018-10-11</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - Redogöra för val av forskningsansats i relation till forskningsfrågor och kuns…</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1385,30 +1385,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2019-04-18</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1418,30 +1418,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>28 ord: - manipulera (söka, lägga till, ändra och ta bort) data och skapa, ändra samt ta…</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1462,19 +1462,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1495,19 +1495,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1528,19 +1528,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GIK2V4</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1550,30 +1550,30 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1583,30 +1583,30 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - Analysera säkerhetsbehov inom ett hemma- eller medelstort företagsnätverk och …</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GIK34Y</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1627,19 +1627,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GIK376</t>
+          <t>GIK34Y</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1649,30 +1649,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK34Y</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GIK3BY</t>
+          <t>GIK376</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1682,30 +1682,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK376</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>IK1032</t>
+          <t>GIK3BY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1715,30 +1715,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2007-06-13</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK3BY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>IK1064</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1748,34 +1748,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2013-02-21</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
+          <t>2007-06-13</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IK1066</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1785,10 +1781,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -1796,29 +1796,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>12 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2020-03-04</t>
+          <t>2013-03-14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1829,19 +1829,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2017-02-16</t>
+          <t>2020-03-04</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1862,29 +1862,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>2017-02-16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat matematikd…</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>26 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda problemområ…</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AMD239</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2055,17 +2055,17 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - visa fördjupad förmåga att självständigt och med relevant teorianvändning anal…</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
+          <t>28 ord: - med utgångspunkt i tidigare forskning identifiera ett väl avgränsat  matematik…</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
+          <t>28 ord: - sammanfatta det matematikdidaktiska forskningsläget inom det valda  problemomr…</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
+          <t>29 ord: - med utgångspunkt i resultaten från den systematiska litteraturstudien i delkur…</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMD2AR</t>
+          <t>AMD239</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2214,34 +2214,30 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2021-12-03</t>
-        </is>
-      </c>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - visa förmåga att självständigt och med relevant teorianvändning analysera och …</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD239</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GMD2GF</t>
+          <t>GMD2AR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2020-04-08</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2020-12-15</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2266,12 +2262,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2AR</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2294,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2315,7 +2311,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GMD2GG</t>
+          <t>GMD2GF</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2335,17 +2331,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GF</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2368,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2389,7 +2385,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GMD2GG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2399,30 +2395,34 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>2020-04-08</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2020-12-15</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - med grund i aktuella styrdokument, forskning och beprövad erfarenhet redogöra …</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2432,14 +2432,10 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2023-04-21</t>
-        </is>
-      </c>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -2447,19 +2443,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2489,14 +2485,14 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GMD2TV</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2506,12 +2502,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2521,19 +2517,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GMD2XQ</t>
+          <t>GMD2TV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2543,10 +2539,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GMD33X</t>
+          <t>GMD2XQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2609,30 +2609,30 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2023-03-17</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>38 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2XQ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GMD33Y</t>
+          <t>GMD33X</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>45 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33X</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
+          <t>77 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MD2022</t>
+          <t>GMD33Y</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2708,23 +2708,23 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2017-09-28</t>
+          <t>2023-03-17</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>37 ord: - beskriva, analysera, diskutera samt tillämpa differentialekvationer av första …</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD33Y</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2747,12 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
+          <t>17 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>MD2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2780,34 +2780,34 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>37 ord: - beskriva, analysera, diskutera och tillämpa differentialekvationer av första o…</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2022</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FMI2222</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
+          <t>2017-09-28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2818,19 +2818,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FMI2223</t>
+          <t>FMI2222</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2017-10-04</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2856,14 +2856,14 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2223</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MIKR002</t>
+          <t>FMI2223</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2873,63 +2873,63 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2012-12-04</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>26 ord: - värdera olika typer av uppgifter och typer av datainsamling med avseende på di…</t>
+          <t>0 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2223</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GMT228</t>
+          <t>MIKR002</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2018-04-05</t>
+          <t>2012-12-04</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - värdera olika typer av uppgifter och typer av datainsamling med avseende på di…</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MIKR002</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GMT343</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2018-04-05</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GMT344</t>
+          <t>GMT343</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3011,24 +3011,24 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>32 ord: - redogöra för centrala begrepp inom området produktionsteknik omfattande område…</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT343</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GMT349</t>
+          <t>GMT344</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3049,19 +3049,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT344</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GMT349</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-04-04</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3082,12 +3082,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>11 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT349</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GMT3BW</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3148,12 +3148,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
+          <t>31 ord: - kritiskt diskutera och reflektera över hur olika typer av materialfel kan påve…</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
+          <t>29 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom statiska- och d…</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GMT3J4</t>
+          <t>GMT3BW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3203,30 +3203,30 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>5 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
+          <t>27 ord: - redogöra för innebörden av begrepp och teoretiska grunder inom energisystem, v…</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3BW</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>GMT3J4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2014-04-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3247,52 +3247,52 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>5 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3J4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>AEG233</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2019-06-05</t>
+          <t>2014-04-03</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
+          <t>10 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AEG294</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3302,30 +3302,30 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2019-06-05</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>6 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
+          <t>28 ord: - analysera och diskutera de fysiska processer som styr utbytet av olika typer a…</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>AEG294</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3335,30 +3335,30 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
+          <t>6 lärandemål (maximum rekommenderat: 4 för 3 hp)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG294</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2015-08-27</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -3379,19 +3379,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
+          <t>28 ord: - analysera och förklara de fysiska processer som styr utbytet hos olika typer a…</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2015-08-27</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -3412,19 +3412,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
+          <t>27 ord: - analysera och diskutera de fysikaliska processer som styr utbytet av en termis…</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>EG3009</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3440,24 +3440,24 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
+          <t>26 ord: - analysera olika metoder som kan användas för att skydda solvärmekretsen för sk…</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3467,23 +3467,23 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2015-08-27</t>
+          <t>2015-09-17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
+          <t>7 lärandemål (maximum rekommenderat: 6 för 5 hp)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
+          <t>35 ord: - ange och självständigt analysera olika sätt att anpassa och designa byggnader …</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
+          <t>28 ord: - Självständigt använda beräkningsprogram och göra beräkningar på en byggnads vä…</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
+          <t>29 ord: - behärska den grundläggande geometrin och vanliga begrepp vad gäller beskrivnin…</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
+          <t>28 ord: - tillämpa beräkningsmodeller och olika instrument för att kunna analysera och a…</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2017-12-14</t>
+          <t>2015-08-27</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3643,19 +3643,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
+          <t>32 ord: - illustrera och reflektera över hur människans behov av dagsljus i byggnader ha…</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>EG3020</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2018-01-25</t>
+          <t>2017-12-14</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3676,19 +3676,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
+          <t>28 ord: - visa kunskap och förståelse inom energieffektivisering, inbegripet såväl överb…</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>EG3022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2014-11-27</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3709,29 +3709,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
+          <t>27 ord: - visa kunskap och förståelse inom solenergiteknik, inbegripet såväl överblick ö…</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSQ23J</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2018-05-24</t>
+          <t>2014-11-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3742,29 +3742,29 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
+          <t>41 ord: - visa väsentligt fördjupade kunskaper och insikter om aktuellt forsknings- och …</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>GSQ23J</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2018-05-24</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3775,19 +3775,19 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
+          <t>30 ord: - Beskriva och analysera den demografiska utvecklingen i Sverige samt vilken bet…</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>AMI23A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3797,14 +3797,10 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2011-02-15</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2012-11-07</t>
-        </is>
-      </c>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -3812,50 +3808,87 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+          <t>38 ord: - visa förståelse för visual literacy, bestämma de grafiska elementen som använd…</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2011-02-15</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2012-11-07</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>2011-12-08</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
         <is>
           <t>Långt mål</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>34 ord: - Visa ett kritiskt förhållningssätt till modellering och analys och att kunna a…</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G102"/>
+  <autoFilter ref="A1:G103"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -4059,6 +4092,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
